--- a/report_template/ABSTRACT_OF_TRUST_FUNDS_COLLECTIONS.xlsx
+++ b/report_template/ABSTRACT_OF_TRUST_FUNDS_COLLECTIONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\2026\ESRE_REPORT\report_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LIFT-LAPTOP\OneDrive\Desktop\ESRE_REPORT\report_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B4F55B-C187-4D28-8C82-9656745B8F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E70CEC-E05C-46B4-89DA-D7D7A140A061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{77777242-AF94-45D7-969D-E74A1D168A0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{77777242-AF94-45D7-969D-E74A1D168A0E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -173,14 +173,103 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -195,123 +284,6 @@
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -370,23 +342,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -395,110 +371,120 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,12 +492,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -520,93 +506,102 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,61 +932,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1000,12 +995,12 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="1"/>
@@ -1033,67 +1028,67 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="8" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="14" t="s">
+      <c r="J7" s="13"/>
+      <c r="K7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="8" t="s">
+      <c r="L7" s="12"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1103,8 +1098,8 @@
       <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1120,12 +1115,17 @@
       <c r="M8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="11"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="N7:N8"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:O3"/>
@@ -1138,11 +1138,6 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="N7:N8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1150,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB422978-B4B8-4ACF-9CBC-2F1251A83AB3}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1166,20 +1161,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="21"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -1195,8 +1190,8 @@
       <c r="K2" s="23"/>
       <c r="L2" s="24"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="27" t="s">
@@ -1219,39 +1214,445 @@
       </c>
       <c r="J3" s="28"/>
       <c r="K3" s="29"/>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="32"/>
+      <c r="B4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="33"/>
+      <c r="L4" s="35"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="37"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="38"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="39"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="39"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="38"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="39"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="39"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="38"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="39"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="38"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="39"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="38"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="39"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="38"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="39"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="38"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="39"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="38"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="39"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="38"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="39"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="39"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="38"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="39"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="38"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="39"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="39"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="39"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="38"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="39"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="38"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="39"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="38"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="39"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="39"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="38"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="39"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="38"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="39"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="39"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="39"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="39"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="38"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="39"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="39"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="40"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="8">
